--- a/kits/pdf-binder/samples/om-handover/output/SAMPLE_Submittal-Log_Harborview-Clinic.xlsx
+++ b/kits/pdf-binder/samples/om-handover/output/SAMPLE_Submittal-Log_Harborview-Clinic.xlsx
@@ -14,6 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Submittal Log'!$A$7:$P$257</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Submittal Log'!$A$1:$P$47</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Submittal Log'!$7:$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
